--- a/outputs/pd_css_cross/gini_curves_model.xlsx
+++ b/outputs/pd_css_cross/gini_curves_model.xlsx
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="50" t="n">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="F9" s="25">
         <f>E9/E29</f>
@@ -4258,10 +4258,10 @@
         <v/>
       </c>
       <c r="D10" s="51" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E10" s="51" t="n">
-        <v>292</v>
+        <v>196</v>
       </c>
       <c r="F10" s="34">
         <f>(E10+E9)/E29</f>
@@ -4392,10 +4392,10 @@
         <v/>
       </c>
       <c r="D11" s="51" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="E11" s="51" t="n">
-        <v>282</v>
+        <v>195</v>
       </c>
       <c r="F11" s="34">
         <f>SUM(E9:E11)/E29</f>
@@ -4525,10 +4525,10 @@
         <v/>
       </c>
       <c r="D12" s="51" t="n">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="E12" s="51" t="n">
-        <v>258</v>
+        <v>197</v>
       </c>
       <c r="F12" s="34">
         <f>SUM(E9:E12)/E29</f>
@@ -4654,10 +4654,10 @@
         <v/>
       </c>
       <c r="D13" s="51" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="E13" s="51" t="n">
-        <v>265</v>
+        <v>187</v>
       </c>
       <c r="F13" s="34">
         <f>SUM(E9:E13)/E29</f>
@@ -4783,10 +4783,10 @@
         <v/>
       </c>
       <c r="D14" s="51" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="E14" s="51" t="n">
-        <v>251</v>
+        <v>169</v>
       </c>
       <c r="F14" s="34">
         <f>SUM(E9:E14)/E29</f>
@@ -4912,10 +4912,10 @@
         <v/>
       </c>
       <c r="D15" s="51" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E15" s="51" t="n">
-        <v>229</v>
+        <v>125</v>
       </c>
       <c r="F15" s="34">
         <f>SUM(E9:E15)/E29</f>
@@ -5041,10 +5041,10 @@
         <v/>
       </c>
       <c r="D16" s="51" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="E16" s="51" t="n">
-        <v>201</v>
+        <v>93</v>
       </c>
       <c r="F16" s="34">
         <f>SUM(E9:E16)/E29</f>
@@ -5170,10 +5170,10 @@
         <v/>
       </c>
       <c r="D17" s="51" t="n">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="E17" s="51" t="n">
-        <v>196</v>
+        <v>73</v>
       </c>
       <c r="F17" s="34">
         <f>SUM(E9:E17)/E29</f>
@@ -5299,10 +5299,10 @@
         <v/>
       </c>
       <c r="D18" s="51" t="n">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E18" s="51" t="n">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="F18" s="34">
         <f>SUM(E9:E18)/E29</f>
@@ -5428,10 +5428,10 @@
         <v/>
       </c>
       <c r="D19" s="51" t="n">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E19" s="51" t="n">
-        <v>140</v>
+        <v>44</v>
       </c>
       <c r="F19" s="34">
         <f>SUM(E9:E19)/E29</f>
@@ -5557,10 +5557,10 @@
         <v/>
       </c>
       <c r="D20" s="51" t="n">
-        <v>185</v>
+        <v>149</v>
       </c>
       <c r="E20" s="51" t="n">
-        <v>112</v>
+        <v>48</v>
       </c>
       <c r="F20" s="34">
         <f>SUM(E9:E20)/E29</f>
@@ -5686,10 +5686,10 @@
         <v/>
       </c>
       <c r="D21" s="51" t="n">
-        <v>200</v>
+        <v>166</v>
       </c>
       <c r="E21" s="51" t="n">
-        <v>97</v>
+        <v>32</v>
       </c>
       <c r="F21" s="34">
         <f>SUM(E9:E21)/E29</f>
@@ -5815,10 +5815,10 @@
         <v/>
       </c>
       <c r="D22" s="51" t="n">
-        <v>235</v>
+        <v>171</v>
       </c>
       <c r="E22" s="51" t="n">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="F22" s="34">
         <f>SUM(E9:E22)/E29</f>
@@ -5944,10 +5944,10 @@
         <v/>
       </c>
       <c r="D23" s="51" t="n">
-        <v>232</v>
+        <v>175</v>
       </c>
       <c r="E23" s="51" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="F23" s="34">
         <f>SUM(E9:E23)/E29</f>
@@ -6073,10 +6073,10 @@
         <v/>
       </c>
       <c r="D24" s="51" t="n">
-        <v>254</v>
+        <v>170</v>
       </c>
       <c r="E24" s="51" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="F24" s="34">
         <f>SUM(E9:E24)/E29</f>
@@ -6202,10 +6202,10 @@
         <v/>
       </c>
       <c r="D25" s="51" t="n">
-        <v>260</v>
+        <v>193</v>
       </c>
       <c r="E25" s="51" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="F25" s="34">
         <f>SUM(E9:E25)/E29</f>
@@ -6331,10 +6331,10 @@
         <v/>
       </c>
       <c r="D26" s="51" t="n">
-        <v>276</v>
+        <v>186</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F26" s="34">
         <f>SUM(E9:E26)/E29</f>
@@ -6460,10 +6460,10 @@
         <v/>
       </c>
       <c r="D27" s="51" t="n">
-        <v>285</v>
+        <v>195</v>
       </c>
       <c r="E27" s="51" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F27" s="34">
         <f>SUM(E9:E27)/E29</f>
@@ -6589,10 +6589,10 @@
         <v/>
       </c>
       <c r="D28" s="52" t="n">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="E28" s="52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F28" s="41">
         <f>SUM(E9:E28)/E29</f>

--- a/outputs/pd_css_cross/gini_curves_model.xlsx
+++ b/outputs/pd_css_cross/gini_curves_model.xlsx
@@ -4128,7 +4128,7 @@
         <v>0</v>
       </c>
       <c r="E9" s="50" t="n">
-        <v>98</v>
+        <v>148</v>
       </c>
       <c r="F9" s="25">
         <f>E9/E29</f>
@@ -4258,10 +4258,10 @@
         <v/>
       </c>
       <c r="D10" s="51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E10" s="51" t="n">
-        <v>196</v>
+        <v>292</v>
       </c>
       <c r="F10" s="34">
         <f>(E10+E9)/E29</f>
@@ -4392,10 +4392,10 @@
         <v/>
       </c>
       <c r="D11" s="51" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="E11" s="51" t="n">
-        <v>195</v>
+        <v>282</v>
       </c>
       <c r="F11" s="34">
         <f>SUM(E9:E11)/E29</f>
@@ -4525,10 +4525,10 @@
         <v/>
       </c>
       <c r="D12" s="51" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="E12" s="51" t="n">
-        <v>197</v>
+        <v>258</v>
       </c>
       <c r="F12" s="34">
         <f>SUM(E9:E12)/E29</f>
@@ -4654,10 +4654,10 @@
         <v/>
       </c>
       <c r="D13" s="51" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="E13" s="51" t="n">
-        <v>187</v>
+        <v>265</v>
       </c>
       <c r="F13" s="34">
         <f>SUM(E9:E13)/E29</f>
@@ -4783,10 +4783,10 @@
         <v/>
       </c>
       <c r="D14" s="51" t="n">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="E14" s="51" t="n">
-        <v>169</v>
+        <v>251</v>
       </c>
       <c r="F14" s="34">
         <f>SUM(E9:E14)/E29</f>
@@ -4912,10 +4912,10 @@
         <v/>
       </c>
       <c r="D15" s="51" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E15" s="51" t="n">
-        <v>125</v>
+        <v>229</v>
       </c>
       <c r="F15" s="34">
         <f>SUM(E9:E15)/E29</f>
@@ -5041,10 +5041,10 @@
         <v/>
       </c>
       <c r="D16" s="51" t="n">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E16" s="51" t="n">
-        <v>93</v>
+        <v>201</v>
       </c>
       <c r="F16" s="34">
         <f>SUM(E9:E16)/E29</f>
@@ -5170,10 +5170,10 @@
         <v/>
       </c>
       <c r="D17" s="51" t="n">
-        <v>124</v>
+        <v>101</v>
       </c>
       <c r="E17" s="51" t="n">
-        <v>73</v>
+        <v>196</v>
       </c>
       <c r="F17" s="34">
         <f>SUM(E9:E17)/E29</f>
@@ -5299,10 +5299,10 @@
         <v/>
       </c>
       <c r="D18" s="51" t="n">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="E18" s="51" t="n">
-        <v>53</v>
+        <v>171</v>
       </c>
       <c r="F18" s="34">
         <f>SUM(E9:E18)/E29</f>
@@ -5428,10 +5428,10 @@
         <v/>
       </c>
       <c r="D19" s="51" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E19" s="51" t="n">
-        <v>44</v>
+        <v>140</v>
       </c>
       <c r="F19" s="34">
         <f>SUM(E9:E19)/E29</f>
@@ -5557,10 +5557,10 @@
         <v/>
       </c>
       <c r="D20" s="51" t="n">
-        <v>149</v>
+        <v>185</v>
       </c>
       <c r="E20" s="51" t="n">
-        <v>48</v>
+        <v>112</v>
       </c>
       <c r="F20" s="34">
         <f>SUM(E9:E20)/E29</f>
@@ -5686,10 +5686,10 @@
         <v/>
       </c>
       <c r="D21" s="51" t="n">
-        <v>166</v>
+        <v>200</v>
       </c>
       <c r="E21" s="51" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="F21" s="34">
         <f>SUM(E9:E21)/E29</f>
@@ -5815,10 +5815,10 @@
         <v/>
       </c>
       <c r="D22" s="51" t="n">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="E22" s="51" t="n">
-        <v>26</v>
+        <v>62</v>
       </c>
       <c r="F22" s="34">
         <f>SUM(E9:E22)/E29</f>
@@ -5944,10 +5944,10 @@
         <v/>
       </c>
       <c r="D23" s="51" t="n">
-        <v>175</v>
+        <v>232</v>
       </c>
       <c r="E23" s="51" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="F23" s="34">
         <f>SUM(E9:E23)/E29</f>
@@ -6073,10 +6073,10 @@
         <v/>
       </c>
       <c r="D24" s="51" t="n">
-        <v>170</v>
+        <v>254</v>
       </c>
       <c r="E24" s="51" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="F24" s="34">
         <f>SUM(E9:E24)/E29</f>
@@ -6202,10 +6202,10 @@
         <v/>
       </c>
       <c r="D25" s="51" t="n">
-        <v>193</v>
+        <v>260</v>
       </c>
       <c r="E25" s="51" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="F25" s="34">
         <f>SUM(E9:E25)/E29</f>
@@ -6331,10 +6331,10 @@
         <v/>
       </c>
       <c r="D26" s="51" t="n">
-        <v>186</v>
+        <v>276</v>
       </c>
       <c r="E26" s="51" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F26" s="34">
         <f>SUM(E9:E26)/E29</f>
@@ -6460,10 +6460,10 @@
         <v/>
       </c>
       <c r="D27" s="51" t="n">
-        <v>195</v>
+        <v>285</v>
       </c>
       <c r="E27" s="51" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F27" s="34">
         <f>SUM(E9:E27)/E29</f>
@@ -6589,10 +6589,10 @@
         <v/>
       </c>
       <c r="D28" s="52" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="E28" s="52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F28" s="41">
         <f>SUM(E9:E28)/E29</f>
